--- a/Result/profitability/2633.xlsx
+++ b/Result/profitability/2633.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM60"/>
+  <dimension ref="A1:AM61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-2.05</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.002500000000000002</v>
+        <v>0.002500000000000002</v>
       </c>
       <c r="N2" t="n">
-        <v>35.04</v>
+        <v>34.97125</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-2.56</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.35375</v>
+        <v>-0.3475</v>
       </c>
       <c r="N3" t="n">
-        <v>27.65125</v>
+        <v>27.435</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.58</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.45625</v>
+        <v>-0.46125</v>
       </c>
       <c r="N4" t="n">
-        <v>25.5925</v>
+        <v>24.95375</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
         <v>-0.5575</v>
       </c>
       <c r="N5" t="n">
-        <v>23.46</v>
+        <v>23.39</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>-0.5</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.65625</v>
+        <v>-0.6537499999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>22.54875</v>
+        <v>22.55</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.02</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.6875</v>
+        <v>-0.6862499999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>22.035</v>
+        <v>21.80625</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -8048,6 +8048,133 @@
       </c>
       <c r="AM60" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2633</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>13922</v>
+      </c>
+      <c r="D61" t="n">
+        <v>8160</v>
+      </c>
+      <c r="E61" t="n">
+        <v>5762</v>
+      </c>
+      <c r="F61" t="n">
+        <v>41.39</v>
+      </c>
+      <c r="G61" t="n">
+        <v>5167</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>37.11%</t>
+        </is>
+      </c>
+      <c r="I61" t="n">
+        <v>-3236</v>
+      </c>
+      <c r="J61" t="n">
+        <v>1931</v>
+      </c>
+      <c r="K61" t="n">
+        <v>1656</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="N61" t="n">
+        <v>43.29375</v>
+      </c>
+      <c r="O61" t="n">
+        <v>1</v>
+      </c>
+      <c r="P61" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>0</v>
+      </c>
+      <c r="R61" t="n">
+        <v>0</v>
+      </c>
+      <c r="S61" t="n">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>0</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
+      </c>
+      <c r="V61" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W61" t="n">
+        <v>-0.08000000000000002</v>
+      </c>
+      <c r="X61" t="n">
+        <v>-0.2162162162162162</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>-5.460000000000001</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>-0.1165421558164355</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC61" t="n">
+        <v>-0.5600000000000023</v>
+      </c>
+      <c r="AD61" t="n">
+        <v>-0.0133492252681765</v>
+      </c>
+      <c r="AE61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK61" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL61" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM61" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
